--- a/app/data/Claim_Input_Template.xlsx
+++ b/app/data/Claim_Input_Template.xlsx
@@ -788,17 +788,17 @@
       </c>
       <c r="C2" s="9" t="inlineStr">
         <is>
-          <t>Bắt buộc</t>
+          <t>Nên có</t>
         </is>
       </c>
       <c r="D2" s="8" t="inlineStr">
         <is>
-          <t>Nhận dòng dữ liệu (dòng có STT là số khác 0); bắt buộc để sinh sheet Pias.</t>
+          <t>Nhận dòng dữ liệu (dòng có STT là số khác 0), loại dòng tổng cộng / ghi chú dưới bảng.</t>
         </is>
       </c>
       <c r="E2" s="8" t="inlineStr">
         <is>
-          <t>Bỏ trống CẢ cột thì vẫn map được (tool chuyển sang nhận dòng theo IMEI/Serial) nhưng sheet Pias ra 0 dòng.</t>
+          <t>Bỏ trống CẢ cột thì tool nhận dòng theo IMEI/Serial, cả khi map lẫn khi sinh sheet Pias; dòng không có IMEI/Serial bị bỏ qua.</t>
         </is>
       </c>
       <c r="F2" s="8" t="inlineStr"/>
